--- a/NY_State_Reports_2026-10-30/Caesars_Sport_Book_Weekly_Report.xlsx
+++ b/NY_State_Reports_2026-10-30/Caesars_Sport_Book_Weekly_Report.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="R:\MOBILE SPORTS WAGERING\11_Weekly Web Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2ECDCA99-276A-4ECF-B4E3-980B6BE92D9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A7A4E88-F80C-49E7-8D14-6930D0323A9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EDA5EF8F-B63B-4D9E-966F-AB4A019BBE74}"/>
   </bookViews>
@@ -2910,7 +2910,12 @@
         <v>46320</v>
       </c>
       <c r="B43" s="19"/>
-      <c r="F43" s="32"/>
+      <c r="C43" s="20">
+        <v>37348683.409999996</v>
+      </c>
+      <c r="F43" s="32">
+        <v>3663823.350000001</v>
+      </c>
       <c r="G43"/>
       <c r="H43"/>
       <c r="I43"/>
@@ -3409,11 +3414,11 @@
       </c>
       <c r="C67" s="22">
         <f>SUM(C13:C66)</f>
-        <v>962514266.50500011</v>
+        <v>999862949.91500008</v>
       </c>
       <c r="F67" s="22">
         <f>SUM(F13:F66)</f>
-        <v>70295014.325000018</v>
+        <v>73958837.675000012</v>
       </c>
       <c r="G67"/>
       <c r="H67"/>
